--- a/大台架材料/VCU相关/VCU接口梳理 - 20260602.xlsx
+++ b/大台架材料/VCU相关/VCU接口梳理 - 20260602.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VCU\VCU_SL_ZhengZhou\ZT2\大台架材料\VCU相关\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="VCU低压电路图" sheetId="1" r:id="rId1"/>
@@ -1171,7 +1176,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1182,6 +1187,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1283,6 +1289,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1344,6 +1359,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1656,11 +1676,11 @@
   <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.4" style="6" customWidth="1"/>
-    <col min="2" max="2" width="16.3333333333333" style="6" customWidth="1"/>
-    <col min="3" max="3" width="32.2666666666667" style="7" customWidth="1"/>
-    <col min="4" max="4" width="14.5333333333333" style="7" customWidth="1"/>
-    <col min="5" max="5" width="45.6666666666667" style="7" customWidth="1"/>
+    <col min="1" max="1" width="13.4" style="7" customWidth="1"/>
+    <col min="2" max="2" width="16.3333333333333" style="7" customWidth="1"/>
+    <col min="3" max="3" width="32.2666666666667" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14.5333333333333" style="8" customWidth="1"/>
+    <col min="5" max="5" width="45.6666666666667" style="8" customWidth="1"/>
     <col min="6" max="6" width="45.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="15.4666666666667" customWidth="1"/>
     <col min="8" max="8" width="18.6666666666667" customWidth="1"/>
@@ -1670,901 +1690,901 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:5">
-      <c r="A2" s="10">
+      <c r="A2" s="11">
         <v>4</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="10"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:5">
-      <c r="A3" s="10">
+      <c r="A3" s="11">
         <v>116</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="10"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="13"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>114</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>115</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="13"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="17">
+      <c r="A7" s="18">
         <v>19</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <v>59</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="19"/>
+      <c r="E7" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="17">
+      <c r="A8" s="18">
         <v>3</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <v>40</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="19">
+      <c r="A9" s="20">
         <v>77</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <v>51</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20" t="s">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="19">
+      <c r="A10" s="20">
         <v>10</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <v>37</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="19">
+      <c r="A11" s="20">
         <v>78</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="20">
         <v>41</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="19">
+      <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="20">
         <v>62</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="19">
+      <c r="A13" s="20">
         <v>76</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>48</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20" t="s">
+      <c r="D13" s="21"/>
+      <c r="E13" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="21">
+      <c r="A14" s="22">
         <v>61</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="22">
         <v>49</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23" t="s">
+      <c r="D14" s="23"/>
+      <c r="E14" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="21">
+      <c r="A15" s="22">
         <v>12</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="22">
         <v>20</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="25"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="21">
+      <c r="A16" s="22">
         <v>60</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="22">
         <v>50</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="24"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="25"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="17">
+      <c r="A17" s="18">
         <v>56</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="18">
         <v>43</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="17">
+      <c r="A18" s="18">
         <v>57</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="18">
         <v>65</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="25"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="17">
+      <c r="A19" s="18">
         <v>86</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <v>26</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="25"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="17">
+      <c r="A20" s="18">
         <v>87</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="18">
         <v>45</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="25"/>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="17">
+      <c r="A21" s="18">
         <v>94</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="18">
         <v>63</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="25"/>
+      <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="17">
+      <c r="A22" s="18">
         <v>95</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="18">
         <v>67</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="25"/>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="17">
+      <c r="A23" s="18">
         <v>96</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <v>68</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="25"/>
+      <c r="E23" s="26"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:11">
-      <c r="A24" s="27">
+      <c r="A24" s="28">
         <v>104</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="28">
         <v>64</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="29"/>
+      <c r="E24" s="30"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:11">
-      <c r="A25" s="27">
+      <c r="A25" s="28">
         <v>111</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="28">
         <v>47</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="29"/>
+      <c r="E25" s="30"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="17">
+      <c r="A26" s="18">
         <v>102</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="18">
         <v>42</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="25"/>
+      <c r="E26" s="26"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="17">
+      <c r="A27" s="18">
         <v>103</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="18">
         <v>52</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="25"/>
+      <c r="E27" s="26"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="17">
+      <c r="A28" s="18">
         <v>29</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="18">
         <v>53</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="17">
+      <c r="A29" s="18">
         <v>31</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="18">
         <v>38</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="17">
+      <c r="A30" s="18">
         <v>32</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="18">
         <v>21</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="17">
+      <c r="A31" s="18">
         <v>33</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="18">
         <v>31</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="17">
+      <c r="A32" s="18">
         <v>34</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="18">
         <v>25</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="31"/>
+      <c r="F32" s="32"/>
       <c r="K32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" s="4" customFormat="1" spans="1:11">
-      <c r="A33" s="32">
+      <c r="A33" s="33">
         <v>68</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="33">
         <v>56</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G33" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="I33" s="35" t="s">
+      <c r="I33" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="K33" s="36" t="s">
+      <c r="K33" s="37" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="34" s="4" customFormat="1" spans="1:11">
-      <c r="A34" s="32">
+      <c r="A34" s="33">
         <v>49</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>55</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="34" t="s">
+      <c r="D34" s="33"/>
+      <c r="E34" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="35" t="s">
+      <c r="G34" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="35" t="s">
+      <c r="I34" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="J34" s="35" t="s">
+      <c r="J34" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="K34" s="36" t="s">
+      <c r="K34" s="37" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" s="4" customFormat="1" spans="1:11">
-      <c r="A35" s="32">
+      <c r="A35" s="33">
         <v>64</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="33">
         <v>57</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="36" t="s">
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="37" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" spans="1:11">
-      <c r="A36" s="32">
+      <c r="A36" s="33">
         <v>45</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="33">
         <v>76</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="34" t="s">
+      <c r="D36" s="33"/>
+      <c r="E36" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="F36" s="35" t="s">
+      <c r="F36" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="36" t="s">
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="37" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="37" s="4" customFormat="1" spans="1:11">
-      <c r="A37" s="32">
+      <c r="A37" s="33">
         <v>69</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="33">
         <v>54</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="36"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="37"/>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:11">
-      <c r="A38" s="32">
+      <c r="A38" s="33">
         <v>50</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <v>73</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="36"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="37"/>
     </row>
     <row r="39" s="5" customFormat="1" spans="1:11">
-      <c r="A39" s="37">
+      <c r="A39" s="38">
         <v>89</v>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="38">
         <v>86</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E39" s="38"/>
-      <c r="F39" s="39" t="s">
+      <c r="E39" s="39"/>
+      <c r="F39" s="40" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" s="5" customFormat="1" spans="1:11">
-      <c r="A40" s="37">
+      <c r="A40" s="38">
         <v>97</v>
       </c>
-      <c r="B40" s="37">
+      <c r="B40" s="38">
         <v>85</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E40" s="38"/>
-      <c r="F40" s="39" t="s">
+      <c r="E40" s="39"/>
+      <c r="F40" s="40" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="21">
+      <c r="A41" s="22">
         <v>90</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="22">
         <v>95</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="41"/>
+      <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="21">
+      <c r="A42" s="22">
         <v>18</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="22">
         <v>96</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="40" t="s">
+      <c r="D42" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="21">
+      <c r="A43" s="22">
         <v>117</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="22">
         <v>110</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="40" t="s">
+      <c r="D43" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="41"/>
+      <c r="E43" s="42"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="21">
+      <c r="A44" s="22">
         <v>118</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="22">
         <v>89</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="41"/>
+      <c r="E44" s="42"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="21">
+      <c r="A45" s="22">
         <v>119</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="22">
         <v>111</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="40" t="s">
+      <c r="D45" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="42"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="21">
+      <c r="A46" s="22">
         <v>120</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="22">
         <v>103</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="41"/>
+      <c r="E46" s="42"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="21">
+      <c r="A47" s="22">
         <v>113</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="22">
         <v>88</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="40" t="s">
+      <c r="D47" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="41"/>
+      <c r="E47" s="42"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="21">
+      <c r="A48" s="22">
         <v>24</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="22">
         <v>109</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="40" t="s">
+      <c r="D48" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="41"/>
-    </row>
-    <row r="49" ht="13.15" customHeight="1" spans="1:5">
-      <c r="A49" s="21">
+      <c r="E48" s="42"/>
+    </row>
+    <row r="49" s="6" customFormat="1" ht="13.15" customHeight="1" spans="1:5">
+      <c r="A49" s="44">
         <v>121</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="44">
         <v>101</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="40" t="s">
+      <c r="D49" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="41" t="s">
+      <c r="E49" s="42" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="21">
+      <c r="A50" s="22">
         <v>59</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <v>106</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="40" t="s">
+      <c r="D50" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="41"/>
+      <c r="E50" s="42"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="21">
+      <c r="A51" s="22">
         <v>98</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="22">
         <v>94</v>
       </c>
-      <c r="C51" s="40" t="s">
+      <c r="C51" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="D51" s="40" t="s">
+      <c r="D51" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="41"/>
+      <c r="E51" s="42"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="21">
+      <c r="A52" s="22">
         <v>37</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <v>114</v>
       </c>
-      <c r="C52" s="40" t="s">
+      <c r="C52" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="41"/>
+      <c r="E52" s="42"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14">
         <v>72</v>
       </c>
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="43" t="s">
+      <c r="D53" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="44" t="s">
+      <c r="E53" s="48" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>35</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <v>98</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="43" t="s">
+      <c r="D54" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="44" t="s">
+      <c r="E54" s="48" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>25</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="D55" s="43"/>
-      <c r="E55" s="44" t="s">
+      <c r="D55" s="47"/>
+      <c r="E55" s="48" t="s">
         <v>128</v>
       </c>
     </row>
